--- a/sheet/EventCardData.xlsx
+++ b/sheet/EventCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFD5B52-5C1A-4DB9-B317-F10A71526DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF96F13-1EFC-40C3-BA01-293D74EFC77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -225,6 +225,30 @@
   </si>
   <si>
     <t>多选：①可重复，支付3金币，从购买能力区选1张牌获得。②可重复至多3次，支付1金币，将购买能力区补满，然后重抽其中任意张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泉水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复一半MP（向下取整）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采石场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗1时间，从遭遇牌堆翻开前2张《水晶》或《金块》，加入背包区。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>废弃营地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗1时间，从遭遇牌堆翻开前2张《木柴捆》，加入背包区。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="32.125" customWidth="1"/>
@@ -678,42 +702,86 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="12" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="57" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+    <row r="13" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
     </row>

--- a/sheet/EventCardData.xlsx
+++ b/sheet/EventCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF96F13-1EFC-40C3-BA01-293D74EFC77D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1E0DF0-C66D-46A1-BA1F-D95B23633D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -171,15 +171,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>地下城重整</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>重抽场上所有敌人侧的牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>翻开遭遇牌堆前3张牌，获得其中1张物品牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -224,31 +216,48 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多选：①可重复，支付3金币，从购买能力区选1张牌获得。②可重复至多3次，支付1金币，将购买能力区补满，然后重抽其中任意张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>泉水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回复一半MP（向下取整）。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>采石场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消耗1时间，从遭遇牌堆翻开前2张《水晶》或《金块》，加入背包区。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>废弃营地</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>消耗1时间，从遭遇牌堆翻开前2张《木柴捆》，加入背包区。</t>
+    <t>重组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从遭遇牌堆翻开第1张《金块》，加入背包区，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从遭遇牌堆翻开第1张《木柴捆》，加入背包区，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复一半MP（向下取整）。&lt;br&gt;
+消耗1时间，从遭遇牌堆翻开第1张《魔瓶》，加入背包区。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹药堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从遭遇牌堆翻开前2张“弹药”牌，加入背包区，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开遭遇牌堆前3张牌，获得其中1张物品牌，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①可重复，支付3金币，从购买能力区选1张牌获得。②可重复，支付1金币，将购买能力区补满，然后重抽其中任意张牌，每次重复该效果，需要支付的金币数量加1。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -627,13 +636,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -642,7 +651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -650,20 +659,20 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="92.25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>3</v>
@@ -674,13 +683,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -691,58 +700,66 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="C10" s="1"/>
+    <row r="10" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
@@ -754,18 +771,18 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -774,15 +791,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/EventCardData.xlsx
+++ b/sheet/EventCardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1E0DF0-C66D-46A1-BA1F-D95B23633D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441B6264-D8A8-41D3-BEE2-0B827E6C74BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -171,10 +171,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>重抽场上所有敌人侧的牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>拉杆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,11 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多选：①弃置1张物品牌。②将1张手牌送墓。③受到2伤害。&lt;br&gt;
-执行2项以上时：从购买能力区选1张牌获得。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>训练场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -209,10 +200,6 @@
   </si>
   <si>
     <t>将弃牌堆顶的1张牌放回主牌堆。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多选：①可重复至多3次，弃置1张物品牌，然后获得1金币。②取遭遇牌堆前3张物品牌，然后玩家每支付2金币，可以获得其中1张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -249,15 +236,36 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>从遭遇牌堆翻开前2张“弹药”牌，加入背包区，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>翻开遭遇牌堆前3张牌，获得其中1张物品牌，再消耗1时间，可以重复1次该效果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多选：①可重复，支付3金币，从购买能力区选1张牌获得。②可重复，支付1金币，将购买能力区补满，然后重抽其中任意张牌，每次重复该效果，需要支付的金币数量加1。</t>
+    <t>重抽场上所有地城阵营的牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从遭遇牌堆翻开第1张“弹药”牌，加入背包区，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①弃置1张物品牌。②将1张手牌送墓。③受到1伤害。&lt;br&gt;
+执行2项以上时：从购买能力区选1张牌获得。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①可重复，出售1张物品牌并获得1金币。②取遭遇牌堆前3张物品牌，然后玩家每支付2金币，可以获得其中1张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①支付8金币，从购买升级区选1张牌获得。②可重复，支付3金币，将购买能力区补满，然后重抽其中任意张牌，每次重复该效果，需要支付的金币数量加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可重复，支付3金币，抽1张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -607,7 +615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="32.125" customWidth="1"/>
@@ -636,13 +644,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -659,20 +667,20 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="92.25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>3</v>
@@ -683,13 +691,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -700,65 +708,65 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -771,18 +779,18 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -793,13 +801,24 @@
     </row>
     <row r="13" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>37</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/EventCardData.xlsx
+++ b/sheet/EventCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441B6264-D8A8-41D3-BEE2-0B827E6C74BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436124DE-1835-4239-AEEA-0BCA9421FFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -179,10 +179,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>获得遭遇牌堆第1张物品牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宝箱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -199,10 +195,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>将弃牌堆顶的1张牌放回主牌堆。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>泉水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -227,45 +219,53 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>回复一半MP（向下取整）。&lt;br&gt;
+    <t>弹药堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重抽场上所有地城阵营的牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从遭遇牌堆翻开第1张“弹药”牌，加入背包区，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>酒馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①支付8金币，从购买升级区选1张牌获得。②可重复，支付3金币，将购买能力区补满，然后重抽其中任意张牌，每次重复该效果，需要支付的金币数量加1。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可重复，支付5金币，抽1张牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复一半MP。&lt;br&gt;
 消耗1时间，从遭遇牌堆翻开第1张《魔瓶》，加入背包区。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>弹药堆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>翻开遭遇牌堆前3张牌，获得其中1张物品牌，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重抽场上所有地城阵营的牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从遭遇牌堆翻开第1张“弹药”牌，加入背包区，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多选：①弃置1张物品牌。②将1张手牌送墓。③受到1伤害。&lt;br&gt;
+    <t>将弃牌堆顶的1张牌放在任意房间的地城侧。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①弃置1张道具牌。②将1张手牌送墓。③受到1伤害。&lt;br&gt;
 执行2项以上时：从购买能力区选1张牌获得。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多选：①可重复，出售1张物品牌并获得1金币。②取遭遇牌堆前3张物品牌，然后玩家每支付2金币，可以获得其中1张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>酒馆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多选：①支付8金币，从购买升级区选1张牌获得。②可重复，支付3金币，将购买能力区补满，然后重抽其中任意张牌，每次重复该效果，需要支付的金币数量加1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可重复，支付3金币，抽1张牌。</t>
+    <t>翻开遭遇牌堆前3张牌，获得其中1张道具牌，再消耗1时间，可以重复1次该效果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得遭遇牌堆第1张道具牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①可重复，出售1张道具牌并获得1金币。②取遭遇牌堆前3张道具牌，然后玩家每支付3金币，可以获得其中1张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,13 +644,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>2</v>
@@ -667,7 +667,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -691,13 +691,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>4</v>
@@ -706,67 +706,67 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -779,18 +779,18 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>5</v>
@@ -801,24 +801,24 @@
     </row>
     <row r="13" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>2</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/EventCardData.xlsx
+++ b/sheet/EventCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436124DE-1835-4239-AEEA-0BCA9421FFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A26AF7F-74F2-4932-B529-CD3E33167DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -265,7 +265,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多选：①可重复，出售1张道具牌并获得1金币。②取遭遇牌堆前3张道具牌，然后玩家每支付3金币，可以获得其中1张牌。</t>
+    <t>多选：①可重复，出售1张道具牌并获得2金币。②取遭遇牌堆前3张道具牌，然后玩家每支付4金币，可以获得其中1张牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/sheet/EventCardData.xlsx
+++ b/sheet/EventCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A26AF7F-74F2-4932-B529-CD3E33167DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3306E39E-6F2E-40FE-BEB7-A87A6ADA6B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>cardName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -51,10 +51,6 @@
   </si>
   <si>
     <t>Lever</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Chest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -138,19 +134,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>① Activate: Add the first two { Loot } cards from the Event Deck to your Loot Zone.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>① Activate, repeatable: Trade 2 non-gold resource for 1 gold or trade 1 gold for 1 non-gold resource. &lt;br&gt;
 ② Activate only when the Player does not have [Wanted] artifact card: Get 1 resource of each type. Then add a [Wanted] card from the Artifact Deck to your Equipment Zone.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>杂物堆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>maxCount</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -167,18 +155,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>祭坛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>拉杆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>选场上1张陷阱牌，触发它或将其移动到场上任意位置。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>宝箱</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -191,81 +171,83 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>足迹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>泉水</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>采石场</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>废弃营地</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从遭遇牌堆翻开第1张《金块》，加入背包区，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从遭遇牌堆翻开第1张《木柴捆》，加入背包区，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弹药堆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重抽场上所有地城阵营的牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>从遭遇牌堆翻开第1张“弹药”牌，加入背包区，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>酒馆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多选：①支付8金币，从购买升级区选1张牌获得。②可重复，支付3金币，将购买能力区补满，然后重抽其中任意张牌，每次重复该效果，需要支付的金币数量加1。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可重复，支付5金币，抽1张牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复一半MP。&lt;br&gt;
-消耗1时间，从遭遇牌堆翻开第1张《魔瓶》，加入背包区。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>将弃牌堆顶的1张牌放在任意房间的地城侧。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>多选：①弃置1张道具牌。②将1张手牌送墓。③受到1伤害。&lt;br&gt;
-执行2项以上时：从购买能力区选1张牌获得。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>翻开遭遇牌堆前3张牌，获得其中1张道具牌，再消耗1时间，可以重复1次该效果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得遭遇牌堆第1张道具牌。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多选：①可重复，出售1张道具牌并获得2金币。②取遭遇牌堆前3张道具牌，然后玩家每支付4金币，可以获得其中1张牌。</t>
+    <t>图书馆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复一半MP。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>召唤石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将楼层区所有牌洗回对应牌堆，然后重置楼层区。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选场上1张陷阱牌，将其移动到楼层区任意房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地城重组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>追踪足迹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得1金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>散落的金币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得2金币。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开升级牌堆前3张技能牌，获得其中1张。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开升级牌堆前3张法术牌，获得其中1张。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神龛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开升级牌堆前3张被动牌，获得其中1张。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开主牌堆前3张怪物牌，选其中1张加入手牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多选：①可重复，出售1张道具牌并获得1金币。②翻开遭遇牌堆前3张道具牌，然后玩家可以支付金币购买其中任意张道具牌，每支付2金币，获得其中1张道具牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>翻开遭遇牌堆前3张牌，获得其中所有道具牌和弹药牌。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -615,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="32.125" customWidth="1"/>
@@ -627,179 +609,173 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:6" ht="92.25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -807,17 +783,6 @@
         <v>2</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
     </row>
